--- a/data/vov.xlsx
+++ b/data/vov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCA9ECE-97A1-A44B-91FB-3692673A0E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FAFAB9-5C0C-2049-BC1F-EF29998D8BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
     <sheet name="Doel" sheetId="6" r:id="rId2"/>
-    <sheet name="Leerplan" sheetId="17" r:id="rId3"/>
+    <sheet name="DoelCollectie" sheetId="17" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,14 +30,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>CODE</t>
   </si>
   <si>
-    <t>ingerichtDoor</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -93,6 +90,9 @@
   </si>
   <si>
     <t>VOV</t>
+  </si>
+  <si>
+    <t>Leerplan</t>
   </si>
 </sst>
 </file>
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -163,6 +163,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,15 +514,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -545,46 +546,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -595,86 +596,92 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7618F3A8-AF47-B947-A911-1EFF15E07583}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="2" width="60" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10"/>
       <c r="B10"/>
       <c r="C10"/>

--- a/data/vov.xlsx
+++ b/data/vov.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FAFAB9-5C0C-2049-BC1F-EF29998D8BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E5B989-23A5-BE4A-888C-7D1CE1D928E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
     <sheet name="Doel" sheetId="6" r:id="rId2"/>
     <sheet name="DoelCollectie" sheetId="17" r:id="rId3"/>
+    <sheet name="_customVoc" sheetId="19" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>CODE</t>
   </si>
@@ -93,13 +94,43 @@
   </si>
   <si>
     <t>Leerplan</t>
+  </si>
+  <si>
+    <t>sheetLabel</t>
+  </si>
+  <si>
+    <t>sheetClass</t>
+  </si>
+  <si>
+    <t>columnLabel</t>
+  </si>
+  <si>
+    <t>columnProperty</t>
+  </si>
+  <si>
+    <t>valueDatatype</t>
+  </si>
+  <si>
+    <t>valueClass</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/Agent</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/title</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2001/XMLSchema#string</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,6 +144,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -148,10 +195,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -163,9 +211,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -635,7 +685,7 @@
       <c r="D2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -691,4 +741,63 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5DBCA2-7850-E34B-B0EF-73419FB83AFE}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{59D7D25F-D92D-E241-81FD-F2ADA2B4A260}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{73DE1675-FF3B-324F-89EB-CB60E68754F7}"/>
+    <hyperlink ref="E2" r:id="rId3" location="string" xr:uid="{FA44FFDA-53E4-AE48-8D11-4CDE41E8003B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/vov.xlsx
+++ b/data/vov.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E5B989-23A5-BE4A-888C-7D1CE1D928E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8272FE97-EC18-4612-819D-83EE557EF0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>CODE</t>
   </si>
@@ -124,13 +124,25 @@
   </si>
   <si>
     <t>http://www.w3.org/2001/XMLSchema#string</t>
+  </si>
+  <si>
+    <t>VOV_SV</t>
+  </si>
+  <si>
+    <t>Leerplannen van het secundair volwassenenonderwijs</t>
+  </si>
+  <si>
+    <t>SV</t>
+  </si>
+  <si>
+    <t>heeftLid</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +173,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -175,7 +194,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -183,42 +202,193 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -229,6 +399,71 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{396F5155-F1EE-4125-9EFF-EDED12E61851}" name="Table2" displayName="Table2" ref="A1:B2" totalsRowShown="0" headerRowDxfId="18" dataDxfId="19">
+  <autoFilter ref="A1:B2" xr:uid="{396F5155-F1EE-4125-9EFF-EDED12E61851}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1B20D69F-EA8D-4902-8229-72D44419C76A}" name="CODE" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{B4B7CE47-DFF6-49BE-872E-8F9C5F8BE7A6}" name="naam" dataDxfId="20"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{89EE2661-E0E5-401B-925F-E5D7F7101ABE}" name="Table3" displayName="Table3" ref="A1:O2" insertRow="1" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+  <autoFilter ref="A1:O2" xr:uid="{89EE2661-E0E5-401B-925F-E5D7F7101ABE}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{7A52802B-F84D-4981-A978-A0A82643616F}" name="CODE" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{392B6A63-79B9-4EB7-BC32-AB65F3EF97C3}" name="beschrijving" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{83FE1FD4-74FA-4D0A-81E6-7FD72CE0AFD3}" name="geldigheid" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{DCA8F1F1-0116-4085-A0AC-E1DAF184529B}" name="identificator" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{647FD3A4-4739-4E93-B3E2-4463470E4C00}" name="niveau" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{7D97D13F-7C43-48ED-9169-7AAD1CA3CECD}" name="gedefinieerdDoor" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{0BC2C49B-D61D-4E16-9DF6-A04B67B647BF}" name="onderwerp" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{85065FDE-E064-4709-B8E4-F619A14D7797}" name="type" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{DE027AAA-6213-4A6E-AA44-31A715273035}" name="bron" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{B8340160-D5B6-45FA-A71A-5502D4B561FA}" name="doelgroep" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{6725B3E7-303A-44E6-B006-D45ED7EA027F}" name="competentie" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{7E282F55-3380-41C8-BE89-8C25E29A0933}" name="gerelateerdAan" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{719BECD9-B17D-4666-B8FC-8582C4A8F813}" name="isSpecialisatieVan" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{034F2D63-BE55-43D7-8028-68D3E9CE051B}" name="isBrederDan" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{684B3EF6-F621-43D8-AB0A-52897A4592AA}" name="bestaatUit" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78E2EF0E-7218-4FDE-8255-C3AC98014B35}" name="Table1" displayName="Table1" ref="A1:F3" totalsRowShown="0" headerRowDxfId="22">
+  <autoFilter ref="A1:F3" xr:uid="{78E2EF0E-7218-4FDE-8255-C3AC98014B35}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{99F58FD3-87F8-4FD4-9D3C-33054FF7AC06}" name="CODE"/>
+    <tableColumn id="2" xr3:uid="{1753F6FC-D04F-4121-898C-9D21CDE65A64}" name="naam"/>
+    <tableColumn id="3" xr3:uid="{E63A3DEF-575F-42F9-87FF-03E3BE089C33}" name="gedefinieerdDoor" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{F9C10B6B-C19E-4B1D-A5E8-7EBAED817E7E}" name="niveau"/>
+    <tableColumn id="5" xr3:uid="{D2BE1EEF-FC77-4C2B-A14D-167717481592}" name="heeftLid"/>
+    <tableColumn id="6" xr3:uid="{71F1F6DA-26C1-4B33-BB8D-2138928160F5}" name="type"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BCE9F56C-6D03-4976-A2AF-6F723F88840C}" name="Table4" displayName="Table4" ref="A1:F2" totalsRowShown="0" headerRowDxfId="0" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:F2" xr:uid="{BCE9F56C-6D03-4976-A2AF-6F723F88840C}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{0FCC0835-BA8A-4965-A58A-C816A8EF1912}" name="sheetLabel"/>
+    <tableColumn id="2" xr3:uid="{D7475D26-9B43-4751-BA50-0F2BF5633093}" name="sheetClass" dataCellStyle="Hyperlink"/>
+    <tableColumn id="3" xr3:uid="{697811BB-15C4-4A3C-8EA3-57A2EDEE17E5}" name="columnLabel"/>
+    <tableColumn id="4" xr3:uid="{F20ACAAA-216B-43C7-B511-0210836D66DD}" name="columnProperty" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{D4EAEF6E-00A4-4B07-94B6-3C04E26FD20F}" name="valueDatatype" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{7B775BB5-E831-4498-A712-94FED6C9AAAF}" name="valueClass"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -554,20 +789,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E48475DD-7AAE-7649-996C-7728C46BB2FB}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="40" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -578,217 +814,237 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="2" width="54.33203125" style="1" customWidth="1"/>
-    <col min="3" max="15" width="40" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="8" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7618F3A8-AF47-B947-A911-1EFF15E07583}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>16</v>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8"/>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9"/>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10"/>
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5DBCA2-7850-E34B-B0EF-73419FB83AFE}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -799,5 +1055,8 @@
     <hyperlink ref="E2" r:id="rId3" location="string" xr:uid="{FA44FFDA-53E4-AE48-8D11-4CDE41E8003B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>